--- a/data/raw/Trading Economics/Markets/Commodities/Industrial/2019~2026_Di-ammonium_CBOT_USD Per Ton.xlsx
+++ b/data/raw/Trading Economics/Markets/Commodities/Industrial/2019~2026_Di-ammonium_CBOT_USD Per Ton.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11640"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11640" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="2019년" sheetId="2" r:id="rId1"/>
@@ -42667,7 +42667,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L140"/>
+  <dimension ref="A1:L175"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -45791,6 +45791,24 @@
       <c r="L125" s="3"/>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A126" s="2">
+        <v>7</v>
+      </c>
+      <c r="B126" s="2">
+        <v>2</v>
+      </c>
+      <c r="C126" s="3">
+        <v>750</v>
+      </c>
+      <c r="D126" s="3">
+        <v>750</v>
+      </c>
+      <c r="E126" s="3">
+        <v>750</v>
+      </c>
+      <c r="F126" s="3">
+        <v>750</v>
+      </c>
       <c r="H126" s="2"/>
       <c r="I126" s="3"/>
       <c r="J126" s="3"/>
@@ -45798,6 +45816,24 @@
       <c r="L126" s="3"/>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A127" s="2">
+        <v>7</v>
+      </c>
+      <c r="B127" s="2">
+        <v>6</v>
+      </c>
+      <c r="C127" s="3">
+        <v>750</v>
+      </c>
+      <c r="D127" s="3">
+        <v>750</v>
+      </c>
+      <c r="E127" s="3">
+        <v>750</v>
+      </c>
+      <c r="F127" s="3">
+        <v>750</v>
+      </c>
       <c r="H127" s="2"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
@@ -45805,65 +45841,999 @@
       <c r="L127" s="3"/>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A128" s="2">
+        <v>7</v>
+      </c>
+      <c r="B128" s="2">
+        <v>7</v>
+      </c>
+      <c r="C128" s="3">
+        <v>750</v>
+      </c>
+      <c r="D128" s="3">
+        <v>750</v>
+      </c>
+      <c r="E128" s="3">
+        <v>750</v>
+      </c>
+      <c r="F128" s="3">
+        <v>750</v>
+      </c>
       <c r="H128" s="2"/>
       <c r="I128" s="3"/>
       <c r="J128" s="3"/>
       <c r="K128" s="3"/>
       <c r="L128" s="3"/>
     </row>
-    <row r="129" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A129" s="2">
+        <v>7</v>
+      </c>
+      <c r="B129" s="2">
+        <v>8</v>
+      </c>
+      <c r="C129" s="3">
+        <v>760</v>
+      </c>
+      <c r="D129" s="3">
+        <v>760</v>
+      </c>
+      <c r="E129" s="3">
+        <v>760</v>
+      </c>
+      <c r="F129" s="3">
+        <v>760</v>
+      </c>
       <c r="H129" s="2"/>
       <c r="I129" s="3"/>
       <c r="J129" s="3"/>
       <c r="K129" s="3"/>
       <c r="L129" s="3"/>
     </row>
-    <row r="130" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A130" s="2">
+        <v>7</v>
+      </c>
+      <c r="B130" s="2">
+        <v>9</v>
+      </c>
+      <c r="C130" s="3">
+        <v>760</v>
+      </c>
+      <c r="D130" s="3">
+        <v>760</v>
+      </c>
+      <c r="E130" s="3">
+        <v>760</v>
+      </c>
+      <c r="F130" s="3">
+        <v>760</v>
+      </c>
       <c r="H130" s="2"/>
       <c r="I130" s="3"/>
       <c r="J130" s="3"/>
       <c r="K130" s="3"/>
       <c r="L130" s="3"/>
     </row>
-    <row r="131" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A131" s="2">
+        <v>7</v>
+      </c>
+      <c r="B131" s="2">
+        <v>10</v>
+      </c>
+      <c r="C131" s="3">
+        <v>765</v>
+      </c>
+      <c r="D131" s="3">
+        <v>765</v>
+      </c>
+      <c r="E131" s="3">
+        <v>765</v>
+      </c>
+      <c r="F131" s="3">
+        <v>765</v>
+      </c>
       <c r="H131" s="3"/>
       <c r="I131" s="3"/>
       <c r="J131" s="3"/>
     </row>
-    <row r="132" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" s="2">
+        <v>7</v>
+      </c>
+      <c r="B132" s="2">
+        <v>13</v>
+      </c>
+      <c r="C132" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="D132" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="E132" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="F132" s="3">
+        <v>767.5</v>
+      </c>
       <c r="H132" s="3"/>
       <c r="I132" s="3"/>
       <c r="J132" s="3"/>
     </row>
-    <row r="133" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" s="2">
+        <v>7</v>
+      </c>
+      <c r="B133" s="2">
+        <v>14</v>
+      </c>
+      <c r="C133" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="D133" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="E133" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="F133" s="3">
+        <v>767.5</v>
+      </c>
       <c r="H133" s="3"/>
       <c r="I133" s="3"/>
       <c r="J133" s="3"/>
     </row>
-    <row r="134" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A134" s="2">
+        <v>7</v>
+      </c>
+      <c r="B134" s="2">
+        <v>15</v>
+      </c>
+      <c r="C134" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="D134" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="E134" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="F134" s="3">
+        <v>767.5</v>
+      </c>
       <c r="H134" s="3"/>
       <c r="I134" s="3"/>
       <c r="J134" s="3"/>
     </row>
-    <row r="135" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" s="2">
+        <v>7</v>
+      </c>
+      <c r="B135" s="2">
+        <v>16</v>
+      </c>
+      <c r="C135" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="D135" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="E135" s="3">
+        <v>767.5</v>
+      </c>
+      <c r="F135" s="3">
+        <v>767.5</v>
+      </c>
       <c r="H135" s="3"/>
       <c r="I135" s="3"/>
       <c r="J135" s="3"/>
     </row>
-    <row r="136" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" s="2">
+        <v>7</v>
+      </c>
+      <c r="B136" s="2">
+        <v>17</v>
+      </c>
+      <c r="C136" s="3">
+        <v>778</v>
+      </c>
+      <c r="D136" s="3">
+        <v>778</v>
+      </c>
+      <c r="E136" s="3">
+        <v>778</v>
+      </c>
+      <c r="F136" s="3">
+        <v>778</v>
+      </c>
       <c r="H136" s="4"/>
     </row>
-    <row r="137" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" s="2">
+        <v>7</v>
+      </c>
+      <c r="B137" s="2">
+        <v>20</v>
+      </c>
+      <c r="C137" s="3">
+        <v>778</v>
+      </c>
+      <c r="D137" s="3">
+        <v>778</v>
+      </c>
+      <c r="E137" s="3">
+        <v>778</v>
+      </c>
+      <c r="F137" s="3">
+        <v>778</v>
+      </c>
       <c r="H137" s="4"/>
     </row>
-    <row r="138" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" s="2">
+        <v>7</v>
+      </c>
+      <c r="B138" s="2">
+        <v>21</v>
+      </c>
+      <c r="C138" s="3">
+        <v>785</v>
+      </c>
+      <c r="D138" s="3">
+        <v>785</v>
+      </c>
+      <c r="E138" s="3">
+        <v>785</v>
+      </c>
+      <c r="F138" s="3">
+        <v>785</v>
+      </c>
       <c r="H138" s="4"/>
     </row>
-    <row r="139" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" s="2">
+        <v>7</v>
+      </c>
+      <c r="B139" s="2">
+        <v>22</v>
+      </c>
+      <c r="C139" s="3">
+        <v>778</v>
+      </c>
+      <c r="D139" s="3">
+        <v>778</v>
+      </c>
+      <c r="E139" s="3">
+        <v>778</v>
+      </c>
+      <c r="F139" s="3">
+        <v>778</v>
+      </c>
       <c r="H139" s="4"/>
     </row>
-    <row r="140" spans="8:12" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" s="2">
+        <v>7</v>
+      </c>
+      <c r="B140" s="2">
+        <v>23</v>
+      </c>
+      <c r="C140" s="3">
+        <v>789</v>
+      </c>
+      <c r="D140" s="3">
+        <v>789</v>
+      </c>
+      <c r="E140" s="3">
+        <v>789</v>
+      </c>
+      <c r="F140" s="3">
+        <v>789</v>
+      </c>
       <c r="H140" s="4"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" s="2">
+        <v>7</v>
+      </c>
+      <c r="B141" s="2">
+        <v>24</v>
+      </c>
+      <c r="C141" s="3">
+        <v>789</v>
+      </c>
+      <c r="D141" s="3">
+        <v>789</v>
+      </c>
+      <c r="E141" s="3">
+        <v>789</v>
+      </c>
+      <c r="F141" s="3">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A142" s="2">
+        <v>7</v>
+      </c>
+      <c r="B142" s="2">
+        <v>27</v>
+      </c>
+      <c r="C142" s="3">
+        <v>791.5</v>
+      </c>
+      <c r="D142" s="3">
+        <v>791.5</v>
+      </c>
+      <c r="E142" s="3">
+        <v>785</v>
+      </c>
+      <c r="F142" s="3">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" s="2">
+        <v>7</v>
+      </c>
+      <c r="B143" s="2">
+        <v>28</v>
+      </c>
+      <c r="C143" s="3">
+        <v>782.5</v>
+      </c>
+      <c r="D143" s="3">
+        <v>800</v>
+      </c>
+      <c r="E143" s="3">
+        <v>782.5</v>
+      </c>
+      <c r="F143" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" s="2">
+        <v>7</v>
+      </c>
+      <c r="B144" s="2">
+        <v>29</v>
+      </c>
+      <c r="C144" s="3">
+        <v>802.5</v>
+      </c>
+      <c r="D144" s="3">
+        <v>802.5</v>
+      </c>
+      <c r="E144" s="3">
+        <v>802.5</v>
+      </c>
+      <c r="F144" s="3">
+        <v>802.5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A145" s="2">
+        <v>7</v>
+      </c>
+      <c r="B145" s="2">
+        <v>30</v>
+      </c>
+      <c r="C145" s="3">
+        <v>802.5</v>
+      </c>
+      <c r="D145" s="3">
+        <v>802.5</v>
+      </c>
+      <c r="E145" s="3">
+        <v>802.5</v>
+      </c>
+      <c r="F145" s="3">
+        <v>802.5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A146" s="2">
+        <v>7</v>
+      </c>
+      <c r="B146" s="2">
+        <v>31</v>
+      </c>
+      <c r="C146" s="3">
+        <v>800</v>
+      </c>
+      <c r="D146" s="3">
+        <v>800</v>
+      </c>
+      <c r="E146" s="3">
+        <v>800</v>
+      </c>
+      <c r="F146" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="2">
+        <v>8</v>
+      </c>
+      <c r="B147" s="2">
+        <v>3</v>
+      </c>
+      <c r="C147" s="3">
+        <v>800</v>
+      </c>
+      <c r="D147" s="3">
+        <v>800</v>
+      </c>
+      <c r="E147" s="3">
+        <v>800</v>
+      </c>
+      <c r="F147" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="2">
+        <v>8</v>
+      </c>
+      <c r="B148" s="2">
+        <v>4</v>
+      </c>
+      <c r="C148" s="3">
+        <v>798</v>
+      </c>
+      <c r="D148" s="3">
+        <v>798</v>
+      </c>
+      <c r="E148" s="3">
+        <v>798</v>
+      </c>
+      <c r="F148" s="3">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="2">
+        <v>8</v>
+      </c>
+      <c r="B149" s="2">
+        <v>5</v>
+      </c>
+      <c r="C149" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D149" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E149" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F149" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="2">
+        <v>8</v>
+      </c>
+      <c r="B150" s="2">
+        <v>6</v>
+      </c>
+      <c r="C150" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D150" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E150" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F150" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A151" s="2">
+        <v>8</v>
+      </c>
+      <c r="B151" s="2">
+        <v>7</v>
+      </c>
+      <c r="C151" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D151" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E151" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F151" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A152" s="2">
+        <v>8</v>
+      </c>
+      <c r="B152" s="2">
+        <v>10</v>
+      </c>
+      <c r="C152" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D152" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E152" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F152" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A153" s="2">
+        <v>8</v>
+      </c>
+      <c r="B153" s="2">
+        <v>11</v>
+      </c>
+      <c r="C153" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D153" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E153" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F153" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A154" s="2">
+        <v>8</v>
+      </c>
+      <c r="B154" s="2">
+        <v>12</v>
+      </c>
+      <c r="C154" s="3">
+        <v>795</v>
+      </c>
+      <c r="D154" s="3">
+        <v>795</v>
+      </c>
+      <c r="E154" s="3">
+        <v>795</v>
+      </c>
+      <c r="F154" s="3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A155" s="2">
+        <v>8</v>
+      </c>
+      <c r="B155" s="2">
+        <v>13</v>
+      </c>
+      <c r="C155" s="3">
+        <v>795</v>
+      </c>
+      <c r="D155" s="3">
+        <v>795</v>
+      </c>
+      <c r="E155" s="3">
+        <v>795</v>
+      </c>
+      <c r="F155" s="3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A156" s="2">
+        <v>8</v>
+      </c>
+      <c r="B156" s="2">
+        <v>14</v>
+      </c>
+      <c r="C156" s="3">
+        <v>795</v>
+      </c>
+      <c r="D156" s="3">
+        <v>795</v>
+      </c>
+      <c r="E156" s="3">
+        <v>795</v>
+      </c>
+      <c r="F156" s="3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A157" s="2">
+        <v>8</v>
+      </c>
+      <c r="B157" s="2">
+        <v>17</v>
+      </c>
+      <c r="C157" s="3">
+        <v>795</v>
+      </c>
+      <c r="D157" s="3">
+        <v>795</v>
+      </c>
+      <c r="E157" s="3">
+        <v>795</v>
+      </c>
+      <c r="F157" s="3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A158" s="2">
+        <v>8</v>
+      </c>
+      <c r="B158" s="2">
+        <v>18</v>
+      </c>
+      <c r="C158" s="3">
+        <v>795</v>
+      </c>
+      <c r="D158" s="3">
+        <v>795</v>
+      </c>
+      <c r="E158" s="3">
+        <v>795</v>
+      </c>
+      <c r="F158" s="3">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A159" s="2">
+        <v>8</v>
+      </c>
+      <c r="B159" s="2">
+        <v>19</v>
+      </c>
+      <c r="C159" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D159" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E159" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F159" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A160" s="2">
+        <v>8</v>
+      </c>
+      <c r="B160" s="2">
+        <v>20</v>
+      </c>
+      <c r="C160" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D160" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E160" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F160" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A161" s="2">
+        <v>8</v>
+      </c>
+      <c r="B161" s="2">
+        <v>21</v>
+      </c>
+      <c r="C161" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D161" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E161" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F161" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A162" s="2">
+        <v>8</v>
+      </c>
+      <c r="B162" s="2">
+        <v>24</v>
+      </c>
+      <c r="C162" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D162" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E162" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F162" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A163" s="2">
+        <v>8</v>
+      </c>
+      <c r="B163" s="2">
+        <v>25</v>
+      </c>
+      <c r="C163" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D163" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E163" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F163" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A164" s="2">
+        <v>8</v>
+      </c>
+      <c r="B164" s="2">
+        <v>26</v>
+      </c>
+      <c r="C164" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D164" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E164" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F164" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A165" s="2">
+        <v>8</v>
+      </c>
+      <c r="B165" s="2">
+        <v>27</v>
+      </c>
+      <c r="C165" s="3">
+        <v>790</v>
+      </c>
+      <c r="D165" s="3">
+        <v>790</v>
+      </c>
+      <c r="E165" s="3">
+        <v>790</v>
+      </c>
+      <c r="F165" s="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A166" s="2">
+        <v>8</v>
+      </c>
+      <c r="B166" s="2">
+        <v>28</v>
+      </c>
+      <c r="C166" s="3">
+        <v>790</v>
+      </c>
+      <c r="D166" s="3">
+        <v>790</v>
+      </c>
+      <c r="E166" s="3">
+        <v>790</v>
+      </c>
+      <c r="F166" s="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A167" s="2">
+        <v>8</v>
+      </c>
+      <c r="B167" s="2">
+        <v>31</v>
+      </c>
+      <c r="C167" s="3">
+        <v>790</v>
+      </c>
+      <c r="D167" s="3">
+        <v>790</v>
+      </c>
+      <c r="E167" s="3">
+        <v>790</v>
+      </c>
+      <c r="F167" s="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A168" s="2">
+        <v>9</v>
+      </c>
+      <c r="B168" s="2">
+        <v>1</v>
+      </c>
+      <c r="C168" s="3">
+        <v>790</v>
+      </c>
+      <c r="D168" s="3">
+        <v>790</v>
+      </c>
+      <c r="E168" s="3">
+        <v>790</v>
+      </c>
+      <c r="F168" s="3">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A169" s="2">
+        <v>9</v>
+      </c>
+      <c r="B169" s="2">
+        <v>2</v>
+      </c>
+      <c r="C169" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D169" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E169" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F169" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A170" s="2">
+        <v>9</v>
+      </c>
+      <c r="B170" s="2">
+        <v>3</v>
+      </c>
+      <c r="C170" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D170" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E170" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F170" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A171" s="2">
+        <v>9</v>
+      </c>
+      <c r="B171" s="2">
+        <v>4</v>
+      </c>
+      <c r="C171" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D171" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E171" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F171" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A172" s="2">
+        <v>9</v>
+      </c>
+      <c r="B172" s="2">
+        <v>8</v>
+      </c>
+      <c r="C172" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="D172" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="E172" s="3">
+        <v>792.5</v>
+      </c>
+      <c r="F172" s="3">
+        <v>792.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A173" s="2">
+        <v>9</v>
+      </c>
+      <c r="B173" s="2">
+        <v>9</v>
+      </c>
+      <c r="C173" s="3">
+        <v>800</v>
+      </c>
+      <c r="D173" s="3">
+        <v>800</v>
+      </c>
+      <c r="E173" s="3">
+        <v>800</v>
+      </c>
+      <c r="F173" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A174" s="2">
+        <v>9</v>
+      </c>
+      <c r="B174" s="2">
+        <v>10</v>
+      </c>
+      <c r="C174" s="3">
+        <v>800</v>
+      </c>
+      <c r="D174" s="3">
+        <v>800</v>
+      </c>
+      <c r="E174" s="3">
+        <v>800</v>
+      </c>
+      <c r="F174" s="3">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A175" s="2">
+        <v>9</v>
+      </c>
+      <c r="B175" s="2">
+        <v>11</v>
+      </c>
+      <c r="C175" s="3">
+        <v>800</v>
+      </c>
+      <c r="D175" s="3">
+        <v>800</v>
+      </c>
+      <c r="E175" s="3">
+        <v>800</v>
+      </c>
+      <c r="F175" s="3">
+        <v>800</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1">
